--- a/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
+++ b/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
@@ -1018,7 +1018,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Every task uses the EDVisits sheet: 937 visits in rows 2–938, columns A–M. For tasks 1–10, sort or filter, then type what you see: an ID, a row number, or a count. Before each filter task, clear the filters left over from the task before (Data → Clear). Tasks 11 and 12 use SUBTOTAL and AGGREGATE while an ESI 3 filter stays on, so do them last. Mac: Ctrl+Shift+L is ⌘+Shift+F.</t>
+          <t>Every task uses the EDVisits sheet: 937 visits in rows 2–938, columns A–M. For tasks 1–10, sort or filter, then type what you see: an ID, a row number, a count, or a value. Before each filter task, clear the filters left over from the task before (Data → Clear). Tasks 11 and 12 use SUBTOTAL and AGGREGATE while an ESI 3 filter stays on, so do them last. Mac: Ctrl+Shift+L is ⌘+Shift+F.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>List range: the ChiefComplaint column only. No criteria range</t>
+          <t>List range: the ChiefComplaint column only. Empty the Criteria range box</t>
         </is>
       </c>
       <c r="D15" s="23" t="n"/>
@@ -51995,6 +51995,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -52519,7 +52521,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="261" customHeight="1">
+    <row r="13" ht="276" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -52542,7 +52544,7 @@
    | ESILevel | DoorToProviderMin |
    | 1 | |
    | | &gt;120 |
-3. Still on Workspace, choose **Data → Advanced**. Select **Copy to another location**. List range: `EDVisits!$A$1:$M$938`. Criteria range: `Workspace!$A$4:$B$6`. Copy to: `Workspace!$D$4`. **OK**.
+3. Still on Workspace, click an empty cell (for example D4), then choose **Data → Advanced**. Select **Copy to another location**. List range: `EDVisits!$A$1:$M$938`. Criteria range: `Workspace!$A$4:$B$6`. Copy to: `Workspace!$D$4`. **OK**.
 4. The copy has a header row plus **65** visit rows.</t>
         </is>
       </c>
@@ -52556,7 +52558,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="186" customHeight="1">
+    <row r="14" ht="201" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -52574,7 +52576,7 @@
         <is>
           <t>1. Click an empty cell on **Workspace** (for example **S4**) and choose **Data → Advanced**.
 2. Select **Copy to another location**. List range: `EDVisits!$H$1:$H$938` (just that one column, header included).
-3. Leave Criteria range empty. Copy to: `Workspace!$S$4`. Tick **Unique records only**. **OK**.
+3. Make the **Criteria range** box empty: Excel may fill in `Workspace!$A$4:$B$6` from task 9, so delete it. Copy to: `Workspace!$S$4`. Tick **Unique records only**. **OK**.
 4. The list has a header plus **28** complaints (select them and read Count on the status bar).</t>
         </is>
       </c>
@@ -52719,7 +52721,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="276" customHeight="1">
+    <row r="5" ht="336" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -52735,13 +52737,13 @@
       </c>
       <c r="D5" s="40" t="inlineStr">
         <is>
-          <t>1. **Data → Clear** on EDVisits. Insert a sheet (**Shift+F11**) and rename it **Review**.
-2. On **Workspace**, build this criteria range in an empty spot (for example A20:C22), with headers copied from EDVisits:
+          <t>1. **Data → Clear** on EDVisits. Insert a sheet with the **+** button next to the sheet tabs (or **Shift+F11**) and rename it **Review**.
+2. On **Workspace**, build this criteria range in an empty spot with a blank column on each side (for example U4:W6, to the right of your task 10 list), with headers copied from EDVisits:
    | ESILevel | ArrivalMode | ArrivalHour |
    |---|---|---|
    | 1 | | |
    | 2 | Ambulance | &gt;=18 |
-3. Click **Review!A1**, then **Data → Advanced** → **Copy to another location**. List range `EDVisits!$A$1:$M$938`, Criteria range `Workspace!$A$20:$C$22`, Copy to `Review!$A$1`. **OK**.
+3. Click **Review!A1**, then **Data → Advanced** → **Copy to another location**. List range `EDVisits!$A$1:$M$938`, Criteria range `Workspace!$U$4:$W$6`, Copy to `Review!$A$1`. **OK**.
 4. Review shows a header plus **60** rows (rows 2–61).</t>
         </is>
       </c>
@@ -52751,7 +52753,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Row 21 of the criteria range (ESILevel = 1) catches all 23 ESI 1 visits. Row 22 is an AND: ESI 2 *and* Ambulance *and* ArrivalHour ≥ 18, which adds 37 more. The two rows together are OR. Excel only copies filtered data to the active sheet, so you must start Data → Advanced from the Review sheet, or Excel shows an error.</t>
+          <t>Row 5 of the criteria range (ESILevel = 1) catches all 23 ESI 1 visits. Row 6 is an AND: ESI 2 *and* Ambulance *and* ArrivalHour ≥ 18, which adds 37 more. The two rows together are OR. Excel only copies filtered data to the active sheet, so you must start Data → Advanced from the Review sheet, or Excel shows an error.</t>
         </is>
       </c>
     </row>
@@ -52818,7 +52820,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="111" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -52834,7 +52836,7 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>1. On Review, press **Ctrl+Shift+L** and filter **ESILevel** to **2**.
+          <t>1. On Review, press **Ctrl+Shift+L** (Mac: **⌘+Shift+F**) and filter **ESILevel** to **2**.
 2. Type `=AGGREGATE(12,5,Review!L2:L61)` in a cell the filter can't hide: row 1, two columns past the data (for example O1), or another sheet.
 3. It returns **19**.</t>
         </is>

--- a/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
+++ b/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
@@ -49,7 +49,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy hh:mm"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +120,11 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -205,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -280,6 +285,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -873,7 +879,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="33" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Note</t>
@@ -881,7 +887,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Use the Workspace sheet for Advanced Filter criteria ranges and results.</t>
+          <t>Use the Workspace sheet for Advanced Filter criteria ranges and results, and for trying the guide's formulas. The gray labels in its row 3 show where each task's cells go.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1024,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Every task uses the EDVisits sheet: 937 visits in rows 2–938, columns A–M. For tasks 1–10, sort or filter, then type what you see: an ID, a row number, a count, or a value. Before each filter task, clear the filters left over from the task before (Data → Clear). Tasks 11 and 12 use SUBTOTAL and AGGREGATE while an ESI 3 filter stays on, so do them last. Mac: Ctrl+Shift+L is ⌘+Shift+F.</t>
+          <t>Every task uses the EDVisits sheet: 937 visits in rows 2–938, columns A–M. For tasks 1–10, sort or filter, then type what you see in the yellow cell: an ID, a row number, a count, or a value. Before each new filter task, clear the filters left over from the task before (Data → Clear). Tasks 9 and 10 use the Workspace sheet. Tasks 11 and 12 need an ESI 3 filter left on, so do them last.</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1120,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Sort by ArrivalDay using the built-in custom list Sun, Mon, Tue, Wed, Thu, Fri, Sat (Sort dialog → Order → Custom List…). On which row does the first Wednesday (Wed) visit appear?</t>
+          <t>Sort by ArrivalDay using the built-in custom list Sun, Mon, Tue, Wed, Thu, Fri, Sat (Sort dialog → Order → Custom List…). On which row does the first Wednesday (Wed) visit appear? Type the row number.</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1136,7 +1142,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Turn on AutoFilter (Ctrl+Shift+L). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
+          <t>Turn on AutoFilter (Ctrl+Shift+L; Mac: ⌘+Shift+F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1163,7 +1169,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Search box at the top of the filter list</t>
+          <t>Type in the Search box, then check which items it ticks before you click OK</t>
         </is>
       </c>
       <c r="D10" s="23" t="n"/>
@@ -1185,7 +1191,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Top 10 hides everything except the largest values</t>
+          <t>After the Top 10 filter, Minimum on the status bar finds the smallest visible wait</t>
         </is>
       </c>
       <c r="D11" s="23" t="n"/>
@@ -1238,7 +1244,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="66" customHeight="1">
+    <row r="14" ht="81" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -1246,7 +1252,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Clear the filters. Use Advanced Filter to find visits that were ESI level 1 OR waited more than 120 minutes for a provider. Build the criteria range on the Workspace sheet and copy the results there (start Data → Advanced from the Workspace sheet). How many visits does it copy?</t>
+          <t>Clear the filters. Use Advanced Filter to find visits that were ESI level 1 OR waited more than 120 minutes for a provider. Type the criteria range in Workspace!A4:B6. Then, with the Workspace sheet active, choose Data → Advanced and copy the results to Workspace!D4. How many visits does it copy? Don't count the header.</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1268,7 +1274,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Use Advanced Filter with Unique records only to copy a list of the different ChiefComplaint values to the Workspace sheet. How many different chief complaints are there? Don't count the header.</t>
+          <t>Use Advanced Filter with Unique records only to copy a list of the different ChiefComplaint values to Workspace!S4. How many different chief complaints are there? Don't count the header.</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1290,7 +1296,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Filter EDVisits to ESILevel 3 only (clear everything else). In the yellow cell, write a formula that averages DoorToProviderMin for the visible rows only, rounded to 1 decimal place with ROUND. Leave the filter on for task 12.</t>
+          <t>Filter EDVisits to ESILevel 3 only, with no other filters on. In the yellow cell, write a formula that averages DoorToProviderMin for the visible rows only, rounded to 1 decimal place with ROUND. Leave the filter on for task 12.</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1312,7 +1318,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Keep the ESI 3 filter on. ShockIndex (HeartRate ÷ SystolicBP) shows #DIV/0! where no blood pressure was recorded, so =SUBTOTAL(104,EDVisits!K2:K938) returns #DIV/0!. Write an AGGREGATE formula that returns the highest ShockIndex among the visible rows while ignoring the errors. (2 decimal places is close enough.)</t>
+          <t>Keep the ESI 3 filter on. ShockIndex (HeartRate ÷ SystolicBP) shows #DIV/0! where no blood pressure was recorded, so =SUBTOTAL(104,EDVisits!K2:K938) returns #DIV/0!. In the yellow cell, write an AGGREGATE formula that returns the highest ShockIndex among the visible rows while ignoring the errors. Don't round it.</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -51971,28 +51977,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
@@ -52002,14 +52008,43 @@
     <row r="1">
       <c r="A1" s="34" t="inlineStr">
         <is>
-          <t>Workspace: build Advanced Filter criteria ranges and results here</t>
+          <t>Workspace: Advanced Filter criteria and results</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Copy header names from row 1 of EDVisits so they match exactly. Keep a blank row or column between a criteria range and other cells. To copy results to this sheet, start Data → Advanced while this sheet is active.</t>
+          <t>Copy header names from row 1 of EDVisits so they match exactly. Start Data → Advanced from this sheet when the results should land here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>Task 9 criteria: A4:B6</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>Task 9 results: copy to D4</t>
+        </is>
+      </c>
+      <c r="S3" s="36" t="inlineStr">
+        <is>
+          <t>Task 10 list: copy to S4</t>
+        </is>
+      </c>
+      <c r="U3" s="36" t="inlineStr">
+        <is>
+          <t>Bonus criteria: U4:W6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Free cells for the guide's examples: A9 and below</t>
         </is>
       </c>
     </row>
@@ -52042,10 +52077,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="79" customHeight="1">
+    <row r="2" ht="94" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Cedar Ridge's ED medical director is preparing a high-acuity review for the quality committee. It covers every ESI 1 visit, plus ESI 2 patients who arrived by ambulance in the evening (ArrivalHour 18 or later, which means 6:00 pm to 11:59 pm). That rule is an OR across different columns, so AutoFilter can't do it in one step. Before you start, clear every filter on EDVisits (Data → Clear). Practice tasks 11 and 12 will turn red, which is expected. Then insert a new sheet named Review, build the criteria range on the Workspace sheet, and use Advanced Filter (started from the Review sheet) to copy the matching rows to Review!A1.</t>
+          <t>Cedar Ridge's ED medical director is preparing a high-acuity review for the quality committee. It covers every ESI 1 visit, plus ESI 2 patients who arrived by ambulance in the evening (ArrivalHour 18 or later, which means 6:00 pm to 11:59 pm). That rule is an OR across different columns, so AutoFilter can't do it in one step. Your practice task 11 and 12 formulas follow the ESI 3 filter, so they switch to ✘ when you clear it. That's expected. To keep them green, first copy each of those two answer cells and paste it back as a value. Then clear every filter on EDVisits (Data → Clear), insert a new sheet named Review, type the criteria range in Workspace!U4:W6, and run Data → Advanced from the Review sheet to copy the matching rows to Review!A1.</t>
         </is>
       </c>
     </row>
@@ -52119,7 +52154,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>What is the average DoorToProviderMin of the review visits, rounded to 1 decimal place?</t>
+          <t>In the yellow cell, write a formula for the average DoorToProviderMin of the review visits, rounded to 1 decimal place.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -52155,7 +52190,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -52163,7 +52198,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>CMS reports ED wait times as medians, because a few very long waits pull an average up. Filter the Review sheet to ESILevel 2 only, then use AGGREGATE to find the median DoorToProviderMin of the visible rows.</t>
+          <t>CMS reports ED wait times as medians, because a few very long waits pull an average up. Filter the Review sheet to ESILevel 2 only. Then, in the yellow cell, write an AGGREGATE formula that returns the median DoorToProviderMin of the visible Review rows.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -52215,52 +52250,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 1.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="126" customHeight="1">
+    <row r="5" ht="156" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>1</t>
@@ -52271,19 +52306,19 @@
           <t>Sort the EDVisits sheet by DoorToProviderMin, Largest to Smallest. Which EDVisitID is now in row 2? (That's the visit with the longest wait from arrival to first provider contact.)</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ED208970</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>1. Click any cell in column L (DoorToProviderMin), for example L2.
-2. Choose **Data → Sort Largest to Smallest** (the Z→A button). Because you clicked a single cell, Excel sorts the whole block of data with it.
+2. Click **Data → Sort Z to A** (the Z→A button). On a number column, the **Home → Sort &amp; Filter** menu calls the same command **Sort Largest to Smallest**. Because you clicked a single cell, Excel sorts the whole block of data with it.
 3. Read A2: **ED208970**, a wait of 299 minutes.</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="41">
+      <c r="E5" cm="1" s="42">
         <f t="array" ref="E5">INDEX('EDVisits'!$A$2:$A$938,MATCH(MAX('EDVisits'!$L$2:$L$938),'EDVisits'!$L$2:$L$938,0))</f>
         <v/>
       </c>
@@ -52304,12 +52339,12 @@
           <t>Use the Sort dialog (Data → Sort) to sort by three levels: ESILevel Smallest to Largest, then DoorToProviderMin Largest to Smallest, then ArrivalDateTime Oldest to Newest. Which EDVisitID is in row 11?</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>ED208106</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>1. Click any cell in the data and choose **Data → Sort**. Check that **My data has headers** is ticked.
 2. Sort by **ESILevel**, Sort On **Cell Values**, Order **Smallest to Largest**.
@@ -52318,7 +52353,7 @@
 5. Read A11: **ED208106**.</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="41">
+      <c r="E6" cm="1" s="42">
         <f t="array" ref="E6">INDEX(_xlfn.SORTBY('EDVisits'!$A$2:$A$938,'EDVisits'!$G$2:$G$938,1,'EDVisits'!$L$2:$L$938,-1,'EDVisits'!$C$2:$C$938,1),10)</f>
         <v/>
       </c>
@@ -52336,13 +52371,13 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Sort by ArrivalDay using the built-in custom list Sun, Mon, Tue, Wed, Thu, Fri, Sat (Sort dialog → Order → Custom List…). On which row does the first Wednesday (Wed) visit appear?</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
+          <t>Sort by ArrivalDay using the built-in custom list Sun, Mon, Tue, Wed, Thu, Fri, Sat (Sort dialog → Order → Custom List…). On which row does the first Wednesday (Wed) visit appear? Type the row number.</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
         <v>433</v>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Sort**. If levels from task 2 are still listed, select each one and click **Delete Level**.
 2. Sort by **ArrivalDay**, Sort On **Cell Values**, Order **Custom List…**.
@@ -52350,7 +52385,7 @@
 4. Scroll down column D until the days change from Tue to Wed: row **433**.</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="41">
+      <c r="E7" cm="1" s="42">
         <f t="array" ref="E7">COUNTIF('EDVisits'!$D$2:$D$938,"Sun")+COUNTIF('EDVisits'!$D$2:$D$938,"Mon")+COUNTIF('EDVisits'!$D$2:$D$938,"Tue")+2</f>
         <v/>
       </c>
@@ -52368,13 +52403,13 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Turn on AutoFilter (Ctrl+Shift+L). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="n">
+          <t>Turn on AutoFilter (Ctrl+Shift+L; Mac: ⌘+Shift+F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
         <v>137</v>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>1. Click any cell in the data and press **Ctrl+Shift+L** (Mac: **⌘+Shift+F**), or choose **Data → Filter**.
 2. Open the **ArrivalMode** arrow, untick **(Select All)**, tick **Ambulance**, **OK**.
@@ -52382,7 +52417,7 @@
 4. The status bar reads **137 of 937 records found**.</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="41">
+      <c r="E8" cm="1" s="42">
         <f t="array" ref="E8">COUNTIFS('EDVisits'!$F$2:$F$938,"Ambulance",'EDVisits'!$G$2:$G$938,"&lt;=2")</f>
         <v/>
       </c>
@@ -52403,10 +52438,10 @@
           <t>Clear the filters (Data → Clear). Use the Search box in the ChiefComplaint filter to show every visit whose complaint contains the word fever anywhere. How many visits are visible?</t>
         </is>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="40" t="n">
         <v>266</v>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Clear** removes the filters from task 4 but keeps the filter arrows.
 2. Open the **ChiefComplaint** arrow and type **fever** in the **Search** box.
@@ -52414,7 +52449,7 @@
 4. The status bar reads **266 of 937 records found**.</t>
         </is>
       </c>
-      <c r="E9" cm="1" s="41">
+      <c r="E9" cm="1" s="42">
         <f t="array" ref="E9">COUNTIF('EDVisits'!$H$2:$H$938,"*fever*")</f>
         <v/>
       </c>
@@ -52424,7 +52459,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1">
+    <row r="10" ht="186" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>6</t>
@@ -52435,18 +52470,18 @@
           <t>Clear the filters. Use Number Filters → Top 10 on DoorToProviderMin to show the 10 longest waits. What is the smallest DoorToProviderMin still visible (the 10th-longest wait), in minutes?</t>
         </is>
       </c>
-      <c r="C10" s="39" t="n">
+      <c r="C10" s="40" t="n">
         <v>160</v>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Clear**.
 2. Open the **DoorToProviderMin** arrow → **Number Filters → Top 10…**.
 3. Leave **Top**, **10**, **Items** and click **OK**.
-4. Ten rows remain. The smallest of them is **160** minutes (sort the column Largest to Smallest to see it at the bottom).</t>
-        </is>
-      </c>
-      <c r="E10" cm="1" s="41">
+4. Ten rows remain. Select L2:L938 and read **Minimum** on the status bar, which skips filtered-out rows (right-click the status bar to turn Minimum on, as in Lesson 1.1). Or sort the column Largest to Smallest and look at the last visible row. Either way it's **160** minutes.</t>
+        </is>
+      </c>
+      <c r="E10" cm="1" s="42">
         <f t="array" ref="E10">LARGE('EDVisits'!$L$2:$L$938,10)</f>
         <v/>
       </c>
@@ -52467,10 +52502,10 @@
           <t>Clear the filters. Show only visits that arrived in November 2025 on a Saturday or Sunday. How many are there?</t>
         </is>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="40" t="n">
         <v>26</v>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Clear**.
 2. Open the **ArrivalDateTime** arrow. In the date tree, untick **(Select All)**, expand **2025**, tick **November**, **OK**. (Or use **Date Filters → All Dates in the Period → November**.)
@@ -52478,7 +52513,7 @@
 4. The status bar reads **26 of 937 records found**.</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="41">
+      <c r="E11" cm="1" s="42">
         <f t="array" ref="E11">SUMPRODUCT((MONTH('EDVisits'!$C$2:$C$938)=11)*(('EDVisits'!$D$2:$D$938="Sat")+('EDVisits'!$D$2:$D$938="Sun")))</f>
         <v/>
       </c>
@@ -52499,10 +52534,10 @@
           <t>Clear the filters. Rows shaded orange are visits that triage flagged as a positive sepsis screen. Filter to the orange rows, then also keep only those with DoorToProviderMin greater than 30. How many flagged visits waited more than 30 minutes to see a provider?</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Clear**.
 2. Open any column's arrow (EDVisitID works) → **Filter by Color** → pick the orange swatch under **Filter by Cell Color**. 68 rows remain.
@@ -52529,26 +52564,26 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Clear the filters. Use Advanced Filter to find visits that were ESI level 1 OR waited more than 120 minutes for a provider. Build the criteria range on the Workspace sheet and copy the results there (start Data → Advanced from the Workspace sheet). How many visits does it copy?</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
+          <t>Clear the filters. Use Advanced Filter to find visits that were ESI level 1 OR waited more than 120 minutes for a provider. Type the criteria range in Workspace!A4:B6. Then, with the Workspace sheet active, choose Data → Advanced and copy the results to Workspace!D4. How many visits does it copy? Don't count the header.</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
         <v>65</v>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>1. **Data → Clear** on EDVisits.
-2. On **Workspace**, type the criteria range in A4:B6:
-   | A | B |
-   |---|---|
-   | ESILevel | DoorToProviderMin |
-   | 1 | |
-   | | &gt;120 |
-3. Still on Workspace, click an empty cell (for example D4), then choose **Data → Advanced**. Select **Copy to another location**. List range: `EDVisits!$A$1:$M$938`. Criteria range: `Workspace!$A$4:$B$6`. Copy to: `Workspace!$D$4`. **OK**.
+2. On **Workspace**, type the criteria range in A4:B6. Copy the two headers from row 1 of EDVisits:
+   | Row | A | B |
+   |:-:|---|---|
+   | 4 | ESILevel | DoorToProviderMin |
+   | 5 | 1 | |
+   | 6 | | &gt;120 |
+3. Still on Workspace, click D4, then choose **Data → Advanced**. Select **Copy to another location**. List range: `EDVisits!$A$1:$M$938`. Criteria range: `Workspace!$A$4:$B$6`. Copy to: `Workspace!$D$4`. **OK**.
 4. The copy has a header row plus **65** visit rows.</t>
         </is>
       </c>
-      <c r="E13" cm="1" s="41">
+      <c r="E13" cm="1" s="42">
         <f t="array" ref="E13">SUMPRODUCT(--((('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$L$2:$L$938&gt;120))&gt;0))</f>
         <v/>
       </c>
@@ -52558,7 +52593,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="201" customHeight="1">
+    <row r="14" ht="186" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -52566,21 +52601,21 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Use Advanced Filter with Unique records only to copy a list of the different ChiefComplaint values to the Workspace sheet. How many different chief complaints are there? Don't count the header.</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="n">
+          <t>Use Advanced Filter with Unique records only to copy a list of the different ChiefComplaint values to Workspace!S4. How many different chief complaints are there? Don't count the header.</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="40" t="inlineStr">
-        <is>
-          <t>1. Click an empty cell on **Workspace** (for example **S4**) and choose **Data → Advanced**.
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>1. On **Workspace**, click **S4** and choose **Data → Advanced**.
 2. Select **Copy to another location**. List range: `EDVisits!$H$1:$H$938` (just that one column, header included).
 3. Make the **Criteria range** box empty: Excel may fill in `Workspace!$A$4:$B$6` from task 9, so delete it. Copy to: `Workspace!$S$4`. Tick **Unique records only**. **OK**.
-4. The list has a header plus **28** complaints (select them and read Count on the status bar).</t>
-        </is>
-      </c>
-      <c r="E14" cm="1" s="41">
+4. The list has a header plus **28** complaints. Select them and read Count on the status bar.</t>
+        </is>
+      </c>
+      <c r="E14" cm="1" s="42">
         <f t="array" ref="E14">SUMPRODUCT(1/COUNTIF('EDVisits'!$H$2:$H$938,'EDVisits'!$H$2:$H$938))</f>
         <v/>
       </c>
@@ -52590,7 +52625,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="156" customHeight="1">
+    <row r="15" ht="171" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -52598,24 +52633,24 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Filter EDVisits to ESILevel 3 only (clear everything else). In the yellow cell, write a formula that averages DoorToProviderMin for the visible rows only, rounded to 1 decimal place with ROUND. Leave the filter on for task 12.</t>
-        </is>
-      </c>
-      <c r="C15" s="42" t="n">
+          <t>Filter EDVisits to ESILevel 3 only, with no other filters on. In the yellow cell, write a formula that averages DoorToProviderMin for the visible rows only, rounded to 1 decimal place with ROUND. Leave the filter on for task 12.</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="n">
         <v>51.7</v>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>=ROUND(SUBTOTAL(101,EDVisits!L2:L938),1)</t>
         </is>
       </c>
-      <c r="E15" cm="1" s="43">
+      <c r="E15" cm="1" s="44">
         <f t="array" ref="E15">ROUND(AVERAGEIFS('EDVisits'!$L$2:$L$938,'EDVisits'!$G$2:$G$938,3),1)</f>
         <v/>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>SUBTOTAL skips rows hidden by a filter, so it averages only the 399 ESI 3 visits. Function 1 would work too, because both 1 and 101 ignore filtered-out rows (101 also ignores rows you hide by hand). AVERAGE-type functions skip blank cells, so the 6 ESI 3 LWBS visits with no wait don't drag the average toward zero. Plain AVERAGE would ignore the filter and average all 922 waits. The key's live cell uses AVERAGEIFS (Lesson 2.5) so it works without a filter. If you clear the filter later, this check turns red, which shows SUBTOTAL responding to the filter.</t>
+          <t>SUBTOTAL skips rows hidden by a filter, so it looks only at the 399 ESI 3 visits. Function 1 would work too, because both 1 and 101 ignore filtered-out rows (101 also ignores rows you hide by hand). AVERAGE-type functions skip blank cells, so the 6 ESI 3 LWBS visits with no wait don't drag the average toward zero. Plain AVERAGE would ignore the filter and average all 922 waits. The key's live cell uses AVERAGEIFS (Lesson 2.5) so it works without a filter. If you clear the filter later, this check turns red, which shows SUBTOTAL responding to the filter. To keep the result, copy the cell and paste it back as a value.</t>
         </is>
       </c>
     </row>
@@ -52627,24 +52662,24 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Keep the ESI 3 filter on. ShockIndex (HeartRate ÷ SystolicBP) shows #DIV/0! where no blood pressure was recorded, so =SUBTOTAL(104,EDVisits!K2:K938) returns #DIV/0!. Write an AGGREGATE formula that returns the highest ShockIndex among the visible rows while ignoring the errors. (2 decimal places is close enough.)</t>
-        </is>
-      </c>
-      <c r="C16" s="44" t="n">
+          <t>Keep the ESI 3 filter on. ShockIndex (HeartRate ÷ SystolicBP) shows #DIV/0! where no blood pressure was recorded, so =SUBTOTAL(104,EDVisits!K2:K938) returns #DIV/0!. In the yellow cell, write an AGGREGATE formula that returns the highest ShockIndex among the visible rows while ignoring the errors. Don't round it.</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="n">
         <v>1.641025641025641</v>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>=AGGREGATE(4,7,EDVisits!K2:K938)</t>
         </is>
       </c>
-      <c r="E16" cm="1" s="45">
+      <c r="E16" cm="1" s="46">
         <f t="array" ref="E16">_xlfn.AGGREGATE(14,6,'EDVisits'!$K$2:$K$938/('EDVisits'!$G$2:$G$938=3),1)</f>
         <v/>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>AGGREGATE(4, 7, range) means MAX (4) while ignoring hidden rows and error values (7). The 6 visible #DIV/0! cells come from LWBS patients whose blood pressure wasn't recorded. SUBTOTAL and MAX return an error as soon as the range holds one, while AGGREGATE steps over it. Option 6 would ignore errors but count the hidden rows, giving the highest shock index of the whole year. A shock index near or above 1.0 suggests the heart is racing to keep blood pressure up, which is why EDs watch it.</t>
+          <t>AGGREGATE(4, 7, range) means MAX (4) while ignoring hidden rows and error values (7). The 6 visible #DIV/0! cells come from LWBS patients whose blood pressure wasn't recorded. SUBTOTAL and MAX return an error as soon as the range holds one, while AGGREGATE steps over it. Option 6 would ignore errors but include the hidden rows, giving the highest shock index of the whole year. A shock index near or above 1.0 suggests the heart is racing to keep blood pressure up, which is why EDs watch it.</t>
         </is>
       </c>
     </row>
@@ -52676,52 +52711,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 1.6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="336" customHeight="1">
+    <row r="5" ht="351" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>B1</t>
@@ -52732,22 +52767,23 @@
           <t>How many visits does your Advanced Filter copy to the Review sheet? Don't count the header row.</t>
         </is>
       </c>
-      <c r="C5" s="39" t="n">
+      <c r="C5" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="40" t="inlineStr">
-        <is>
-          <t>1. **Data → Clear** on EDVisits. Insert a sheet with the **+** button next to the sheet tabs (or **Shift+F11**) and rename it **Review**.
-2. On **Workspace**, build this criteria range in an empty spot with a blank column on each side (for example U4:W6, to the right of your task 10 list), with headers copied from EDVisits:
-   | ESILevel | ArrivalMode | ArrivalHour |
-   |---|---|---|
-   | 1 | | |
-   | 2 | Ambulance | &gt;=18 |
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>1. **Data → Clear** on EDVisits. Insert a sheet with the **+** button next to the sheet tabs (or press **Shift+F11**; on a Mac laptop, **Fn+Shift+F11**), then double-click its tab and rename it **Review**.
+2. On **Workspace**, type this criteria range in U4:W6, to the right of your task 10 list. Copy the headers from row 1 of EDVisits:
+   | Row | U | V | W |
+   |:-:|---|---|---|
+   | 4 | ESILevel | ArrivalMode | ArrivalHour |
+   | 5 | 1 | | |
+   | 6 | 2 | Ambulance | &gt;=18 |
 3. Click **Review!A1**, then **Data → Advanced** → **Copy to another location**. List range `EDVisits!$A$1:$M$938`, Criteria range `Workspace!$U$4:$W$6`, Copy to `Review!$A$1`. **OK**.
 4. Review shows a header plus **60** rows (rows 2–61).</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="41">
+      <c r="E5" cm="1" s="42">
         <f t="array" ref="E5">SUMPRODUCT((('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18)))</f>
         <v/>
       </c>
@@ -52765,18 +52801,18 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>What is the average DoorToProviderMin of the review visits, rounded to 1 decimal place?</t>
-        </is>
-      </c>
-      <c r="C6" s="42" t="n">
+          <t>In the yellow cell, write a formula for the average DoorToProviderMin of the review visits, rounded to 1 decimal place.</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="n">
         <v>15.8</v>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>`=ROUND(AVERAGE(Review!L2:L61),1)` (or `=ROUND(AVERAGE(Review!L:L),1)`, because AVERAGE skips the text header).</t>
         </is>
       </c>
-      <c r="E6" cm="1" s="43">
+      <c r="E6" cm="1" s="44">
         <f t="array" ref="E6">ROUND(SUMPRODUCT((('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))*ISNUMBER('EDVisits'!$L$2:$L$938),'EDVisits'!$L$2:$L$938)/SUMPRODUCT((('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))*ISNUMBER('EDVisits'!$L$2:$L$938)),1)</f>
         <v/>
       </c>
@@ -52797,12 +52833,12 @@
           <t>The director lists dispositions by level of care. Create the custom list Admitted, Observation, Transferred, Discharged, Left AMA, LWBS. Sort the Review sheet by EDDisposition with that list, then by DoorToProviderMin Largest to Smallest. Which EDVisitID is in row 44 of the Review sheet?</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>ED207754</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>1. On Review, click any cell in the data → **Data → Sort**. Sort by **EDDisposition**, Order **Custom List…**.
 2. Select **NEW LIST**, type the six entries one per line (press Enter after each), click **Add**, then **OK**.
@@ -52810,7 +52846,7 @@
 4. Rows 2–43 hold the 42 Admitted visits, so row 44 is the first Observation visit: **ED207754**.</t>
         </is>
       </c>
-      <c r="E7" cm="1" s="41">
+      <c r="E7" cm="1" s="42">
         <f t="array" ref="E7">INDEX(_xlfn.SORTBY(_xlfn._xlws.FILTER('EDVisits'!$A$2:$A$938,(('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))),_xlfn.XMATCH(_xlfn._xlws.FILTER('EDVisits'!$M$2:$M$938,(('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))),{"Admitted","Observation","Transferred","Discharged","Left AMA","LWBS"}),1,_xlfn._xlws.FILTER('EDVisits'!$L$2:$L$938,(('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))),-1),43)</f>
         <v/>
       </c>
@@ -52828,20 +52864,20 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>CMS reports ED wait times as medians, because a few very long waits pull an average up. Filter the Review sheet to ESILevel 2 only, then use AGGREGATE to find the median DoorToProviderMin of the visible rows.</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="n">
+          <t>CMS reports ED wait times as medians, because a few very long waits pull an average up. Filter the Review sheet to ESILevel 2 only. Then, in the yellow cell, write an AGGREGATE formula that returns the median DoorToProviderMin of the visible Review rows.</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
         <v>19</v>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>1. On Review, press **Ctrl+Shift+L** (Mac: **⌘+Shift+F**) and filter **ESILevel** to **2**.
-2. Type `=AGGREGATE(12,5,Review!L2:L61)` in a cell the filter can't hide: row 1, two columns past the data (for example O1), or another sheet.
+2. In the yellow B4 cell on the Bonus sheet, type `=AGGREGATE(12,5,Review!L2:L61)`. The Bonus sheet isn't filtered, so the filter can't hide your formula.
 3. It returns **19**.</t>
         </is>
       </c>
-      <c r="E8" cm="1" s="41">
+      <c r="E8" cm="1" s="42">
         <f t="array" ref="E8">MEDIAN(IF((('EDVisits'!$G$2:$G$938=1)+('EDVisits'!$G$2:$G$938=2)*('EDVisits'!$F$2:$F$938="Ambulance")*('EDVisits'!$E$2:$E$938&gt;=18))*('EDVisits'!$G$2:$G$938=2)*ISNUMBER('EDVisits'!$L$2:$L$938),'EDVisits'!$L$2:$L$938))</f>
         <v/>
       </c>

--- a/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
+++ b/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C30"/>
+  <dimension ref="B2:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -716,7 +716,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner  ·  about 45 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner  ·  about 110 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -935,34 +935,58 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>12 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>EDVisits</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Data: 937 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="63" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>All 937 emergency department visits at Cedar Ridge Medical Center in 2025: arrival time, day and hour, arrival mode, ESI triage level, chief complaint, two triage vital signs, a shock index formula, door-to-provider minutes, and disposition. Rows shaded orange were flagged by the triage sepsis screen.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (4 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="63" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>All 937 emergency department visits at Cedar Ridge Medical Center in 2025: arrival time, day and hour, arrival mode, ESI triage level, chief complaint, two triage vital signs, a shock index formula, door-to-provider minutes, and disposition. Rows shaded orange were flagged by the triage sepsis screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
+++ b/01-foundations/06-sorting-filtering/1.6-sorting-filtering.xlsx
@@ -796,7 +796,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -804,7 +804,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. For tasks 1–10, sort or filter the EDVisits sheet, then type what you see into the yellow cell. For tasks 11 and 12, type a formula.</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EDVisits is a plain range on purpose (not an Excel Table), so you turn AutoFilter on yourself with Ctrl+Shift+L (Mac: ⌘+Shift+F). Rows shaded orange were flagged by the triage sepsis screen.</t>
+          <t>EDVisits is a plain range on purpose (not an Excel Table), so you turn AutoFilter on yourself with Ctrl + Shift + L (Mac: ⌘ + Shift + F). Rows shaded orange were flagged by the triage sepsis screen.</t>
         </is>
       </c>
     </row>
@@ -868,91 +868,91 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Use the Workspace sheet for Advanced Filter criteria ranges and results, and for trying the guide's formulas. The gray labels in its row 3 show where each task's cells go.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Your answer goes here.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Yellow cell</t>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>✔ Correct</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Your answer goes here.</t>
+          <t>Your answer matches the key.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>✔ Correct</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>✘ Not yet</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Your answer matches the key.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>✘ Not yet</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
           <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Sheets in this workbook</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>12 practice tasks, each with a Check cell.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>EDVisits</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>12 practice tasks, each with a Check cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
+          <t>Data: 937 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>EDVisits</t>
+          <t>Workspace</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 937 rows</t>
+          <t>Your work area for the Advanced Filter criteria ranges and results (tasks 9–10 and the bonus) and for trying the guide's formulas. The gray labels in its row 3 show where each task's cells go.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>4</t>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Turn on AutoFilter (Ctrl+Shift+L; Mac: ⌘+Shift+F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
+          <t>Turn on AutoFilter with Ctrl + Shift + L (Mac: ⌘ + Shift + F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -52404,7 +52404,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Turn on AutoFilter (Ctrl+Shift+L; Mac: ⌘+Shift+F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
+          <t>Turn on AutoFilter with Ctrl + Shift + L (Mac: ⌘ + Shift + F). Show only visits with ArrivalMode = Ambulance and ESILevel 1 or 2. How many visits are visible?</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
@@ -52412,7 +52412,7 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>1. Click any cell in the data and press Ctrl+Shift+L (Mac: ⌘+Shift+F), or choose Data → Filter.
+          <t>1. Click any cell in the data and press Ctrl + Shift + L (Mac: ⌘ + Shift + F), or choose Data → Filter.
 2. Open the ArrivalMode arrow, untick (Select All), tick Ambulance, OK.
 3. Open the ESILevel arrow, untick 3, 4 and 5 (or use Number Filters → Less Than Or Equal To → 2), OK.
 4. The status bar reads 137 of 937 records found.</t>
@@ -52773,7 +52773,7 @@
       </c>
       <c r="D5" s="40" t="inlineStr">
         <is>
-          <t>1. Data → Clear on EDVisits. Insert a sheet with the + button next to the sheet tabs (or press Shift+F11; on a Mac laptop, Fn+Shift+F11), then double-click its tab and rename it Review.
+          <t>1. Data → Clear on EDVisits. Insert a sheet with the + button next to the sheet tabs (or press Shift + F11; on a Mac laptop, Fn + Shift + F11), then double-click its tab and rename it Review.
 2. On Workspace, type this criteria range in U4:W6, to the right of your task 10 list. Copy the headers from row 1 of EDVisits:
    | Row | U | V | W |
    |:-:|---|---|---|
@@ -52873,7 +52873,7 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>1. On Review, press Ctrl+Shift+L (Mac: ⌘+Shift+F) and filter ESILevel to 2.
+          <t>1. On Review, press Ctrl + Shift + L (Mac: ⌘ + Shift + F) and filter ESILevel to 2.
 2. In the yellow B4 cell on the Bonus sheet, type =AGGREGATE(12,5,Review!L2:L61). The Bonus sheet isn't filtered, so the filter can't hide your formula.
 3. It returns 19.</t>
         </is>
